--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>146</v>
+        <v>264</v>
       </c>
       <c r="D2">
-        <v>124</v>
+        <v>159</v>
       </c>
       <c r="E2">
-        <v>126</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>81</v>
+        <v>223</v>
       </c>
       <c r="D3">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="E3">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="D2">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="D3">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H3">
         <v>426</v>
